--- a/data/out/best_models_lstm/in/best_models_lstm_v2.xlsx
+++ b/data/out/best_models_lstm/in/best_models_lstm_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\out\best_models_lstm\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D88F07-B863-40D7-94DE-67A58244236B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949CE2AE-4E19-43B8-B308-F3584E4E26C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="38">
   <si>
     <t>variant</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>train_time_s</t>
-  </si>
-  <si>
-    <t>v1_original</t>
   </si>
   <si>
     <t>LSTM</t>
@@ -459,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -505,526 +502,526 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>0.45519661903381348</v>
+        <v>0.88744527101516724</v>
       </c>
       <c r="E2">
-        <v>220.09748840332031</v>
+        <v>82.078758239746094</v>
       </c>
       <c r="F2">
-        <v>136973.046875</v>
+        <v>28312.8359375</v>
       </c>
       <c r="G2">
-        <v>370.09869384765619</v>
+        <v>168.2641906738281</v>
       </c>
       <c r="H2">
-        <v>104.5032262802124</v>
+        <v>160.98654270172119</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>48168</v>
+        <v>48144</v>
       </c>
       <c r="K2">
-        <v>38534</v>
+        <v>38515</v>
       </c>
       <c r="L2">
-        <v>9634</v>
+        <v>9629</v>
       </c>
       <c r="M2">
-        <v>134.57122302055359</v>
+        <v>158.81152009963989</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
       <c r="D3">
-        <v>0.88744527101516724</v>
+        <v>0.41212993860244751</v>
       </c>
       <c r="E3">
-        <v>82.078758239746094</v>
+        <v>230.55718994140619</v>
       </c>
       <c r="F3">
-        <v>28312.8359375</v>
+        <v>147800.765625</v>
       </c>
       <c r="G3">
-        <v>168.2641906738281</v>
+        <v>384.44863891601563</v>
       </c>
       <c r="H3">
-        <v>160.98654270172119</v>
+        <v>97.975242137908936</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>48144</v>
+        <v>48168</v>
       </c>
       <c r="K3">
-        <v>38515</v>
+        <v>38534</v>
       </c>
       <c r="L3">
-        <v>9629</v>
+        <v>9634</v>
       </c>
       <c r="M3">
-        <v>158.81152009963989</v>
+        <v>126.8517305850983</v>
+      </c>
+      <c r="Q3">
+        <v>347.02</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4">
-        <v>0.41212993860244751</v>
+        <v>0.85218322277069092</v>
       </c>
       <c r="E4">
-        <v>230.55718994140619</v>
+        <v>90.472953796386719</v>
       </c>
       <c r="F4">
-        <v>147800.765625</v>
+        <v>37182.9140625</v>
       </c>
       <c r="G4">
-        <v>384.44863891601563</v>
+        <v>192.82872009277341</v>
       </c>
       <c r="H4">
-        <v>97.975242137908936</v>
+        <v>166.3738489151001</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4">
-        <v>48168</v>
+        <v>48144</v>
       </c>
       <c r="K4">
-        <v>38534</v>
+        <v>38515</v>
       </c>
       <c r="L4">
-        <v>9634</v>
+        <v>9629</v>
       </c>
       <c r="M4">
-        <v>126.8517305850983</v>
-      </c>
-      <c r="Q4">
-        <v>347.02</v>
+        <v>86.930367469787598</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5">
-        <v>0.85218322277069092</v>
+        <v>0.45648270845413208</v>
       </c>
       <c r="E5">
-        <v>90.472953796386719</v>
+        <v>215.66072082519531</v>
       </c>
       <c r="F5">
-        <v>37182.9140625</v>
+        <v>136649.71875</v>
       </c>
       <c r="G5">
-        <v>192.82872009277341</v>
+        <v>369.66162109375</v>
       </c>
       <c r="H5">
-        <v>166.3738489151001</v>
+        <v>101.634693145752</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>48144</v>
+        <v>48168</v>
       </c>
       <c r="K5">
-        <v>38515</v>
+        <v>38534</v>
       </c>
       <c r="L5">
-        <v>9629</v>
+        <v>9634</v>
       </c>
       <c r="M5">
-        <v>86.930367469787598</v>
+        <v>77.303448915481567</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6">
-        <v>0.45648270845413208</v>
+        <v>0.85910916328430176</v>
       </c>
       <c r="E6">
-        <v>215.66072082519531</v>
+        <v>89.730636596679688</v>
       </c>
       <c r="F6">
-        <v>136649.71875</v>
+        <v>35440.7109375</v>
       </c>
       <c r="G6">
-        <v>369.66162109375</v>
+        <v>188.25703430175781</v>
       </c>
       <c r="H6">
-        <v>101.634693145752</v>
+        <v>160.69958209991461</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>48168</v>
+        <v>48144</v>
       </c>
       <c r="K6">
-        <v>38534</v>
+        <v>38515</v>
       </c>
       <c r="L6">
-        <v>9634</v>
+        <v>9629</v>
       </c>
       <c r="M6">
-        <v>77.303448915481567</v>
+        <v>79.885785579681396</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7">
-        <v>0.85910916328430176</v>
+        <v>0.3719295859336853</v>
       </c>
       <c r="E7">
-        <v>89.730636596679688</v>
+        <v>229.09417724609381</v>
       </c>
       <c r="F7">
-        <v>35440.7109375</v>
+        <v>157907.84375</v>
       </c>
       <c r="G7">
-        <v>188.25703430175781</v>
+        <v>397.37619018554688</v>
       </c>
       <c r="H7">
-        <v>160.69958209991461</v>
+        <v>99.921846389770508</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7">
-        <v>48144</v>
+        <v>48168</v>
       </c>
       <c r="K7">
-        <v>38515</v>
+        <v>38534</v>
       </c>
       <c r="L7">
-        <v>9629</v>
+        <v>9634</v>
       </c>
       <c r="M7">
-        <v>79.885785579681396</v>
+        <v>136.78057074546811</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
       </c>
       <c r="D8">
-        <v>0.3719295859336853</v>
+        <v>0.86569839715957642</v>
       </c>
       <c r="E8">
-        <v>229.09417724609381</v>
+        <v>91.438316345214844</v>
       </c>
       <c r="F8">
-        <v>157907.84375</v>
+        <v>33783.2109375</v>
       </c>
       <c r="G8">
-        <v>397.37619018554688</v>
+        <v>183.8020935058594</v>
       </c>
       <c r="H8">
-        <v>99.921846389770508</v>
+        <v>162.699294090271</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>48168</v>
+        <v>48144</v>
       </c>
       <c r="K8">
-        <v>38534</v>
+        <v>38515</v>
       </c>
       <c r="L8">
-        <v>9634</v>
+        <v>9629</v>
       </c>
       <c r="M8">
-        <v>136.78057074546811</v>
+        <v>78.516274929046631</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9">
-        <v>0.86569839715957642</v>
+        <v>0.25096374750137329</v>
       </c>
       <c r="E9">
-        <v>91.438316345214844</v>
+        <v>251.1893005371094</v>
       </c>
       <c r="F9">
-        <v>33783.2109375</v>
+        <v>188320.75</v>
       </c>
       <c r="G9">
-        <v>183.8020935058594</v>
+        <v>433.95938110351563</v>
       </c>
       <c r="H9">
-        <v>162.699294090271</v>
+        <v>93.235546350479126</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9">
-        <v>48144</v>
+        <v>48168</v>
       </c>
       <c r="K9">
-        <v>38515</v>
+        <v>38534</v>
       </c>
       <c r="L9">
-        <v>9629</v>
+        <v>9634</v>
       </c>
       <c r="M9">
-        <v>78.516274929046631</v>
+        <v>379.61443328857422</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
       </c>
       <c r="D10">
-        <v>0.25096374750137329</v>
+        <v>0.88075011968612671</v>
       </c>
       <c r="E10">
-        <v>251.1893005371094</v>
+        <v>82.908363342285156</v>
       </c>
       <c r="F10">
-        <v>188320.75</v>
+        <v>29996.990234375</v>
       </c>
       <c r="G10">
-        <v>433.95938110351563</v>
+        <v>173.19639587402341</v>
       </c>
       <c r="H10">
-        <v>93.235546350479126</v>
+        <v>161.52176856994629</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10">
-        <v>48168</v>
+        <v>48144</v>
       </c>
       <c r="K10">
-        <v>38534</v>
+        <v>38515</v>
       </c>
       <c r="L10">
-        <v>9634</v>
+        <v>9629</v>
       </c>
       <c r="M10">
-        <v>379.61443328857422</v>
+        <v>78.952606201171875</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11">
-        <v>0.88075011968612671</v>
+        <v>3.3320367336273193E-2</v>
       </c>
       <c r="E11">
-        <v>82.908363342285156</v>
+        <v>294.36236572265619</v>
       </c>
       <c r="F11">
-        <v>29996.990234375</v>
+        <v>243040.09375</v>
       </c>
       <c r="G11">
-        <v>173.19639587402341</v>
+        <v>492.990966796875</v>
       </c>
       <c r="H11">
-        <v>161.52176856994629</v>
+        <v>83.160728216171265</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11">
-        <v>48144</v>
+        <v>48168</v>
       </c>
       <c r="K11">
-        <v>38515</v>
+        <v>38534</v>
       </c>
       <c r="L11">
-        <v>9629</v>
+        <v>9634</v>
       </c>
       <c r="M11">
-        <v>78.952606201171875</v>
+        <v>72.386467218399048</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12">
-        <v>3.3320367336273193E-2</v>
+        <v>0.8641890287399292</v>
       </c>
       <c r="E12">
-        <v>294.36236572265619</v>
+        <v>83.943336486816406</v>
       </c>
       <c r="F12">
-        <v>243040.09375</v>
+        <v>34162.890625</v>
       </c>
       <c r="G12">
-        <v>492.990966796875</v>
+        <v>184.8320617675781</v>
       </c>
       <c r="H12">
-        <v>83.160728216171265</v>
+        <v>165.173864364624</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12">
-        <v>48168</v>
+        <v>48144</v>
       </c>
       <c r="K12">
-        <v>38534</v>
+        <v>38515</v>
       </c>
       <c r="L12">
-        <v>9634</v>
+        <v>9629</v>
       </c>
       <c r="M12">
-        <v>72.386467218399048</v>
+        <v>78.423354387283325</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>0.8641890287399292</v>
+        <v>0.48857390880584722</v>
       </c>
       <c r="E13">
-        <v>83.943336486816406</v>
+        <v>206.6275634765625</v>
       </c>
       <c r="F13">
-        <v>34162.890625</v>
+        <v>128581.421875</v>
       </c>
       <c r="G13">
-        <v>184.8320617675781</v>
+        <v>358.58251953125</v>
       </c>
       <c r="H13">
-        <v>165.173864364624</v>
+        <v>132.8768968582153</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13">
-        <v>48144</v>
+        <v>48168</v>
       </c>
       <c r="K13">
-        <v>38515</v>
+        <v>38534</v>
       </c>
       <c r="L13">
-        <v>9629</v>
+        <v>9634</v>
       </c>
       <c r="M13">
-        <v>78.423354387283325</v>
+        <v>301.39894032478333</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>0.48857390880584722</v>
+        <v>0.51532936096191406</v>
       </c>
       <c r="E14">
-        <v>206.6275634765625</v>
+        <v>188.10406494140619</v>
       </c>
       <c r="F14">
-        <v>128581.421875</v>
+        <v>121854.6328125</v>
       </c>
       <c r="G14">
-        <v>358.58251953125</v>
+        <v>349.07684326171881</v>
       </c>
       <c r="H14">
-        <v>132.8768968582153</v>
+        <v>137.98140287399289</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14">
         <v>48168</v>
@@ -1036,36 +1033,36 @@
         <v>9634</v>
       </c>
       <c r="M14">
-        <v>301.39894032478333</v>
+        <v>1434.510687351227</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>31</v>
       </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
       <c r="D15">
-        <v>0.51532936096191406</v>
+        <v>0.4549528956413269</v>
       </c>
       <c r="E15">
-        <v>188.10406494140619</v>
+        <v>200.5406188964844</v>
       </c>
       <c r="F15">
-        <v>121854.6328125</v>
+        <v>137034.328125</v>
       </c>
       <c r="G15">
-        <v>349.07684326171881</v>
+        <v>370.18148803710938</v>
       </c>
       <c r="H15">
-        <v>137.98140287399289</v>
+        <v>127.63477563858029</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15">
         <v>48168</v>
@@ -1077,36 +1074,36 @@
         <v>9634</v>
       </c>
       <c r="M15">
-        <v>1434.510687351227</v>
+        <v>419.80159163475042</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16">
-        <v>0.4549528956413269</v>
+        <v>0.46174365282058721</v>
       </c>
       <c r="E16">
-        <v>200.5406188964844</v>
+        <v>193.62431335449219</v>
       </c>
       <c r="F16">
-        <v>137034.328125</v>
+        <v>135327.015625</v>
       </c>
       <c r="G16">
-        <v>370.18148803710938</v>
+        <v>367.86819458007813</v>
       </c>
       <c r="H16">
-        <v>127.63477563858029</v>
+        <v>127.2269368171692</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16">
         <v>48168</v>
@@ -1118,211 +1115,170 @@
         <v>9634</v>
       </c>
       <c r="M16">
-        <v>419.80159163475042</v>
+        <v>1347.9657783508301</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
       </c>
       <c r="D17">
-        <v>0.46174365282058721</v>
+        <v>-0.84072399139404297</v>
       </c>
       <c r="E17">
-        <v>193.62431335449219</v>
+        <v>110.9495162963867</v>
       </c>
       <c r="F17">
-        <v>135327.015625</v>
+        <v>17757.03515625</v>
       </c>
       <c r="G17">
-        <v>367.86819458007813</v>
+        <v>133.2555236816406</v>
       </c>
       <c r="H17">
-        <v>127.2269368171692</v>
+        <v>103.23276519775391</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J17">
-        <v>48168</v>
+        <v>13081</v>
       </c>
       <c r="K17">
-        <v>38534</v>
+        <v>10464</v>
       </c>
       <c r="L17">
-        <v>9634</v>
+        <v>2617</v>
       </c>
       <c r="M17">
-        <v>1347.9657783508301</v>
+        <v>21.66329383850098</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
       </c>
       <c r="D18">
-        <v>-0.84072399139404297</v>
+        <v>-0.33871150016784668</v>
       </c>
       <c r="E18">
-        <v>110.9495162963867</v>
+        <v>97.200897216796875</v>
       </c>
       <c r="F18">
-        <v>17757.03515625</v>
+        <v>12935.7255859375</v>
       </c>
       <c r="G18">
-        <v>133.2555236816406</v>
+        <v>113.73532867431641</v>
       </c>
       <c r="H18">
-        <v>103.23276519775391</v>
+        <v>91.481506824493408</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18">
-        <v>13081</v>
+        <v>13057</v>
       </c>
       <c r="K18">
-        <v>10464</v>
+        <v>10445</v>
       </c>
       <c r="L18">
-        <v>2617</v>
+        <v>2612</v>
       </c>
       <c r="M18">
-        <v>21.66329383850098</v>
+        <v>23.890466928482059</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
         <v>35</v>
       </c>
       <c r="D19">
-        <v>-0.33871150016784668</v>
+        <v>4.2700231075286872E-2</v>
       </c>
       <c r="E19">
-        <v>97.200897216796875</v>
+        <v>63.778976440429688</v>
       </c>
       <c r="F19">
-        <v>12935.7255859375</v>
+        <v>9234.84765625</v>
       </c>
       <c r="G19">
-        <v>113.73532867431641</v>
+        <v>96.098114013671875</v>
       </c>
       <c r="H19">
-        <v>91.481506824493408</v>
+        <v>54.979008436203003</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J19">
-        <v>13057</v>
+        <v>13081</v>
       </c>
       <c r="K19">
-        <v>10445</v>
+        <v>10464</v>
       </c>
       <c r="L19">
-        <v>2612</v>
+        <v>2617</v>
       </c>
       <c r="M19">
-        <v>23.890466928482059</v>
+        <v>37.305931806564331</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20">
-        <v>4.2700231075286872E-2</v>
+        <v>5.5243313312530518E-2</v>
       </c>
       <c r="E20">
-        <v>63.778976440429688</v>
+        <v>67.74285888671875</v>
       </c>
       <c r="F20">
-        <v>9234.84765625</v>
+        <v>9129.0126953125</v>
       </c>
       <c r="G20">
-        <v>96.098114013671875</v>
+        <v>95.545867919921875</v>
       </c>
       <c r="H20">
-        <v>54.979008436203003</v>
+        <v>68.008005619049072</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20">
-        <v>13081</v>
+        <v>13057</v>
       </c>
       <c r="K20">
-        <v>10464</v>
+        <v>10445</v>
       </c>
       <c r="L20">
-        <v>2617</v>
+        <v>2612</v>
       </c>
       <c r="M20">
-        <v>37.305931806564331</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21">
-        <v>5.5243313312530518E-2</v>
-      </c>
-      <c r="E21">
-        <v>67.74285888671875</v>
-      </c>
-      <c r="F21">
-        <v>9129.0126953125</v>
-      </c>
-      <c r="G21">
-        <v>95.545867919921875</v>
-      </c>
-      <c r="H21">
-        <v>68.008005619049072</v>
-      </c>
-      <c r="I21" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21">
-        <v>13057</v>
-      </c>
-      <c r="K21">
-        <v>10445</v>
-      </c>
-      <c r="L21">
-        <v>2612</v>
-      </c>
-      <c r="M21">
         <v>24.058205604553219</v>
       </c>
     </row>
